--- a/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="94">
   <si>
     <t>Result</t>
   </si>
@@ -309,6 +309,15 @@
   </si>
   <si>
     <t>Thu Jul 09 23:00:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:36:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:37:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:38:05 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -715,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -732,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -749,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNnoMatch.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="94">
   <si>
     <t>Result</t>
   </si>
@@ -309,6 +309,15 @@
   </si>
   <si>
     <t>Thu Jul 09 23:00:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:14:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:14:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:15:04 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -715,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -732,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -749,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
